--- a/output/pdf_financials_xlsx/DTC.xlsx
+++ b/output/pdf_financials_xlsx/DTC.xlsx
@@ -679,7 +679,7 @@
         <v>-13.193045</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3.522072</v>
+        <v>-3.522072</v>
       </c>
     </row>
     <row r="17">
@@ -755,7 +755,7 @@
         <v>-13.193045</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.522072</v>
+        <v>-3.522072</v>
       </c>
     </row>
     <row r="21">
@@ -803,7 +803,7 @@
         <v>-13.193045</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3.522072</v>
+        <v>-3.522072</v>
       </c>
     </row>
     <row r="24">
@@ -851,7 +851,7 @@
         <v>43.976817</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-50.315314</v>
+        <v>50.315314</v>
       </c>
     </row>
     <row r="27">
@@ -867,7 +867,7 @@
         <v>-13.193045</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.522072</v>
+        <v>-3.522072</v>
       </c>
     </row>
     <row r="28">
@@ -899,7 +899,7 @@
         <v>-13.193045</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.522072</v>
+        <v>-3.522072</v>
       </c>
     </row>
     <row r="30">
@@ -937,7 +937,7 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1914,13 +1914,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.38708</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>6.877146</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.753396</v>
       </c>
     </row>
     <row r="93">
@@ -3090,7 +3090,11 @@
           <t>Share-based payments reserve (note 11)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3377,7 +3381,11 @@
           <t>Share-based Payments Reserve (note 11)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>1.38708</v>
       </c>
@@ -5019,7 +5027,7 @@
         <v>-13.193045</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>3.522072</v>
+        <v>-3.522072</v>
       </c>
     </row>
     <row r="79">

--- a/output/pdf_financials_xlsx/DTC.xlsx
+++ b/output/pdf_financials_xlsx/DTC.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.006809</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.021886</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>6.3e-05</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.867783</v>
+        <v>-6.874592</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-13.193045</v>
+        <v>-13.214931</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.522072</v>
+        <v>-3.522135</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.867783</v>
+        <v>-6.874592</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-13.193045</v>
+        <v>-13.214931</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.522072</v>
+        <v>-3.522135</v>
       </c>
     </row>
     <row r="30">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.792931</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.056547</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.792931</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.056547</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.285106</v>
+        <v>0.492175</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.061082</v>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">

--- a/output/pdf_financials_xlsx/DTC.xlsx
+++ b/output/pdf_financials_xlsx/DTC.xlsx
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.065803</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.203239</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.065803</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.203239</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-7.657428</v>
+        <v>-7.723231</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-4.28838</v>
+        <v>-4.491619</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-3.400218</v>
@@ -3805,7 +3805,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -4225,7 +4229,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>-0.105</v>
       </c>
@@ -4256,7 +4264,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
         <v>-0.065803</v>
       </c>
@@ -4318,7 +4330,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>8.24865</v>
       </c>
